--- a/forms/trg/Formulir_TRG_psyling.xlsx
+++ b/forms/trg/Formulir_TRG_psyling.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ikhwan M. Said, M.Hum</t>
+          <t>Prof. Dr. Nurhayati, M.Hum</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,22 +928,18 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Semantik</t>
+          <t>Psikolinguistik</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-7102-2256</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>56471534100</t>
+          <t>57136752300</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rismayanti, M.Hum</t>
+          <t>Dr. Ikhwan M. Said, M.Hum</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,16 +969,24 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Stilistika</t>
+          <t>Semantik</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-7102-2256</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>56471534100</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -995,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hj. Indarwati, S.S., M.Hum.</t>
+          <t>Rismayanti, M.Hum</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1010,24 +1014,16 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Sosiolinguistik</t>
+          <t>Stilistika</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9205-7933</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>58771987000</t>
-        </is>
-      </c>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1040,31 +1036,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Manavave Mamah</t>
+          <t>Dr. Hj. Indarwati, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Yala Rajabath University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>(Doctoral/Magister/GRaduate)</t>
+          <t>Sosiolinguistik</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9205-7933</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>58771987000</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1077,22 +1081,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Alexandra Tilman, M.A.</t>
+          <t>Manavave Mamah</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>National University of Timor Leste</t>
+          <t>Yala Rajabath University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>literature</t>
+          <t>(Doctoral/Magister/GRaduate)</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1114,39 +1118,31 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nurhayati, M.Hum</t>
+          <t>Alexandra Tilman, M.A.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universitas</t>
+          <t>National University of Timor Leste</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Psikolinguistik</t>
+          <t>literature</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>http://https://orcid.org/0000-0001-6447-0018</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57136752300</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1159,22 +1155,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ikhwan Said, M.Hum</t>
+          <t>Prof. Dr. Nurhayati, M.Hum</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Universitas</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Semantik</t>
+          <t>Psikolinguistik</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1183,13 +1179,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7102-2256</t>
+          <t>http://https://orcid.org/0000-0001-6447-0018</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>56471534100</t>
+          <t>57136752300</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1204,12 +1200,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Rismayanti, S.S., M.Hum</t>
+          <t>Dr. Ikhwan Said, M.Hum</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1219,16 +1215,24 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Stilistika</t>
+          <t>Semantik</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-7102-2256</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>56471534100</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1241,12 +1245,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hj. Indarwati, S.S., M.Hum.</t>
+          <t>Rismayanti, S.S., M.Hum</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1256,18 +1260,14 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Sosiolinguistik</t>
+          <t>Stilistika</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9205-7933</t>
-        </is>
-      </c>
+      <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ayumi Luthfiana N</t>
+          <t>Dr. Hj. Indarwati, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1297,14 +1297,18 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>(GRaduate)</t>
+          <t>Sosiolinguistik</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9205-7933</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
@@ -1319,22 +1323,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Gilang Ramadan</t>
+          <t>Ayumi Luthfiana N</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hsanuddin</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Magister</t>
+          <t>(GRaduate)</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1356,22 +1360,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Andi Haikal Bangsawan</t>
+          <t>Gilang Ramadan</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Universitas Hsanuddin</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>PSYCHOLINGUISTICS Team</t>
+          <t>Magister</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1391,10 +1395,26 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Andi Haikal Bangsawan</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Graduate</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>PSYCHOLINGUISTICS Team</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1402,7 +1422,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1591,15 +1615,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
